--- a/.claude/projects/202607_불닭_MX실견적_v1.xlsx
+++ b/.claude/projects/202607_불닭_MX실견적_v1.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="견적서(안B_권장)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="시나리오비교" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별투입_안B(9-12월)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +74,29 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BBBBBB"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +123,28 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE0F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -168,11 +210,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00333333"/>
+      </right>
+      <top style="thin">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,6 +288,42 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1342,4 +1434,339 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>불닭닷컴 리뉴얼 · MX실 M/M 산정 (9월 착수~12월 · 안B 권장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>52% 할인 후 최종 97,390,000원(VAT별도) · 총 11.0 M/M · UI Design(MX매출) 7.0MM/4,905만</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>파트</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>M/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="37">
+        <f>SUM(D5:G5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>기획</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>중급</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="37">
+        <f>SUM(D6:G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>CD (UI)</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>고급</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H7" s="37">
+        <f>SUM(D7:G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>Designer (UI)</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>중급</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="37">
+        <f>SUM(D8:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Designer (UI)</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="37">
+        <f>SUM(D9:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>2D 모셔너·프로토타입 (UI)</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>초급</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="37">
+        <f>SUM(D10:G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>월별 투입 / 총합</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="42">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="42">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="42">
+        <f>SUM(F5:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="42">
+        <f>SUM(G5:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="43">
+        <f>SUM(H5:H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>[산정] SW산업협회 2026 · 개발비=DL+제경비(110%)+기술료((DL+제경비)×20%) · 52% 할인 후 만원 절사(VAT별도)
+[MX 축소] 타부서 21.5MM 대비 기획 슬림+퍼블/개발 제외+핵심집중+AI공수절감 → 11MM. 비정형·바이럴·2D모션 유지.
+[리스크] 9월 착수=실디자인 4개월 압축. BI(8월)·사진(9~10월)과 병행. 페이지 우선순위·소스 적시전달 전제, 미확보시 단계분리(2a/2b).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A13:H16"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>